--- a/data/trans_bre/P68-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P68-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 4,4</t>
+          <t>-13,2; 4,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 6,22</t>
+          <t>-15,67; 5,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-26,41; -1,94</t>
+          <t>-28,88; -0,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 26,21</t>
+          <t>-3,08; 25,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,3; 16,4</t>
+          <t>-41,07; 15,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,54; 23,28</t>
+          <t>-42,48; 20,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-61,49; -5,14</t>
+          <t>-62,66; -0,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 143,33</t>
+          <t>-14,31; 147,43</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,2; -0,87</t>
+          <t>-9,42; -1,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 3,07</t>
+          <t>-6,19; 3,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,02; -1,46</t>
+          <t>-10,18; -1,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 19,32</t>
+          <t>0,84; 21,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,89; -3,37</t>
+          <t>-34,13; -4,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-25,1; 13,68</t>
+          <t>-23,46; 13,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,4; -6,17</t>
+          <t>-38,69; -7,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 160,79</t>
+          <t>5,22; 183,17</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 10,43</t>
+          <t>-2,12; 10,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 12,87</t>
+          <t>-2,14; 11,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 12,37</t>
+          <t>-0,44; 12,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 10,18</t>
+          <t>-0,83; 9,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,2; 66,16</t>
+          <t>-11,14; 67,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 110,08</t>
+          <t>-13,16; 99,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 80,0</t>
+          <t>-1,68; 81,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 81,76</t>
+          <t>-4,63; 77,13</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 0,33</t>
+          <t>-6,42; -0,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 3,41</t>
+          <t>-4,08; 3,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,38; -0,33</t>
+          <t>-7,34; -0,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 14,3</t>
+          <t>2,07; 15,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 1,28</t>
+          <t>-24,45; -0,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 15,27</t>
+          <t>-16,54; 13,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,97; -1,4</t>
+          <t>-27,49; -1,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,17; 107,58</t>
+          <t>11,67; 117,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P68-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P68-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,88</t>
+          <t>5,57</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 4,47</t>
+          <t>-12,6; 4,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 5,7</t>
+          <t>-14,85; 5,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,88; -0,7</t>
+          <t>-26,28; -0,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 25,74</t>
+          <t>-4,7; 16,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,07; 15,89</t>
+          <t>-40,08; 15,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,48; 20,23</t>
+          <t>-41,5; 19,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-62,66; -0,67</t>
+          <t>-60,68; -0,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 147,43</t>
+          <t>-18,48; 91,25</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,06</t>
+          <t>2,27</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,42; -1,18</t>
+          <t>-9,78; -1,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 3,13</t>
+          <t>-6,43; 2,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,18; -1,7</t>
+          <t>-9,87; -1,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 21,26</t>
+          <t>-1,33; 5,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,13; -4,1</t>
+          <t>-35,38; -4,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,46; 13,89</t>
+          <t>-24,27; 13,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,69; -7,5</t>
+          <t>-36,92; -5,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,22; 183,17</t>
+          <t>-5,61; 29,68</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 10,32</t>
+          <t>-2,26; 10,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 11,69</t>
+          <t>-1,78; 11,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 12,77</t>
+          <t>-1,14; 12,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 9,95</t>
+          <t>-0,91; 9,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 67,28</t>
+          <t>-10,62; 69,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 99,46</t>
+          <t>-10,71; 100,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 81,45</t>
+          <t>-6,16; 83,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 77,13</t>
+          <t>-5,27; 70,93</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,03</t>
+          <t>2,88</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,42; -0,09</t>
+          <t>-6,81; -0,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 3,1</t>
+          <t>-4,23; 3,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,34; -0,32</t>
+          <t>-7,23; -0,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 15,06</t>
+          <t>0,22; 5,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,45; -0,08</t>
+          <t>-26,05; -1,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 13,79</t>
+          <t>-17,02; 13,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,49; -1,28</t>
+          <t>-26,97; -0,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,67; 117,1</t>
+          <t>0,67; 31,28</t>
         </is>
       </c>
     </row>
